--- a/06_GD32F407_FreeRTOS_MutexSemaphore/Project/GD32F407_analysis.xlsx
+++ b/06_GD32F407_FreeRTOS_MutexSemaphore/Project/GD32F407_analysis.xlsx
@@ -500,103 +500,103 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>24.53242492675781</c:v>
+                  <c:v>24.50093078613281</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.23234176635742</c:v>
+                  <c:v>15.0587329864502</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.639244079589844</c:v>
+                  <c:v>6.630720615386963</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.15720796585083</c:v>
+                  <c:v>6.149303436279297</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.035092353820801</c:v>
+                  <c:v>6.027344703674316</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.936049938201904</c:v>
+                  <c:v>5.212144374847412</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.267626285552979</c:v>
+                  <c:v>4.262147903442383</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.804871797561646</c:v>
+                  <c:v>3.799987077713013</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.779163122177124</c:v>
+                  <c:v>3.774311542510986</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.624911546707153</c:v>
+                  <c:v>3.620258092880249</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.43209719657898</c:v>
+                  <c:v>3.427691221237183</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.020759582519531</c:v>
+                  <c:v>3.016881704330444</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.789382457733154</c:v>
+                  <c:v>2.785801410675049</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.750819444656372</c:v>
+                  <c:v>2.74728798866272</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.851018667221069</c:v>
+                  <c:v>1.848642349243164</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.761038661003113</c:v>
+                  <c:v>1.758777856826782</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.156886696815491</c:v>
+                  <c:v>1.155401468276978</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.9640722274780273</c:v>
+                  <c:v>0.9628345966339111</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.629860520362854</c:v>
+                  <c:v>0.6290519237518311</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.617006242275238</c:v>
+                  <c:v>0.6162141561508179</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.308503121137619</c:v>
+                  <c:v>0.3081070780754089</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2313773334026337</c:v>
+                  <c:v>0.2310802936553955</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2313773334026337</c:v>
+                  <c:v>0.2310802936553955</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2313773334026337</c:v>
+                  <c:v>0.2310802936553955</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2056687474250794</c:v>
+                  <c:v>0.2054047137498856</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1928144544363022</c:v>
+                  <c:v>0.19256691634655</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1928144544363022</c:v>
+                  <c:v>0.19256691634655</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1928144544363022</c:v>
+                  <c:v>0.19256691634655</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.07712578028440476</c:v>
+                  <c:v>0.07702676951885223</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.05141718685626984</c:v>
+                  <c:v>0.05135117843747139</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.05141718685626984</c:v>
+                  <c:v>0.05135117843747139</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.02570859342813492</c:v>
+                  <c:v>0.0256755892187357</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.02570859342813492</c:v>
+                  <c:v>0.0256755892187357</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0</c:v>
@@ -1173,10 +1173,10 @@
         <v>64</v>
       </c>
       <c r="D7" s="1">
-        <v>2370</v>
+        <v>2346</v>
       </c>
       <c r="E7" s="1">
-        <v>2350</v>
+        <v>2326</v>
       </c>
       <c r="F7" s="1">
         <v>20</v>
@@ -1225,10 +1225,10 @@
         <v>24</v>
       </c>
       <c r="D9" s="1">
-        <v>768</v>
+        <v>812</v>
       </c>
       <c r="E9" s="1">
-        <v>768</v>
+        <v>812</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>24.53242492675781</v>
+        <v>24.50093078613281</v>
       </c>
       <c r="C3" s="1">
         <v>3817</v>
@@ -1456,16 +1456,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>15.23234176635742</v>
+        <v>15.0587329864502</v>
       </c>
       <c r="C4" s="1">
-        <v>2370</v>
+        <v>2346</v>
       </c>
       <c r="D4" s="1">
         <v>64</v>
       </c>
       <c r="E4" s="1">
-        <v>2350</v>
+        <v>2326</v>
       </c>
       <c r="F4" s="1">
         <v>20</v>
@@ -1482,7 +1482,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>6.639244079589844</v>
+        <v>6.630720615386963</v>
       </c>
       <c r="C5" s="1">
         <v>1033</v>
@@ -1508,7 +1508,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>6.15720796585083</v>
+        <v>6.149303436279297</v>
       </c>
       <c r="C6" s="1">
         <v>958</v>
@@ -1534,7 +1534,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>6.035092353820801</v>
+        <v>6.027344703674316</v>
       </c>
       <c r="C7" s="1">
         <v>939</v>
@@ -1560,16 +1560,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>4.936049938201904</v>
+        <v>5.212144374847412</v>
       </c>
       <c r="C8" s="1">
-        <v>768</v>
+        <v>812</v>
       </c>
       <c r="D8" s="1">
         <v>24</v>
       </c>
       <c r="E8" s="1">
-        <v>768</v>
+        <v>812</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>4.267626285552979</v>
+        <v>4.262147903442383</v>
       </c>
       <c r="C9" s="1">
         <v>664</v>
@@ -1612,7 +1612,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>3.804871797561646</v>
+        <v>3.799987077713013</v>
       </c>
       <c r="C10" s="1">
         <v>592</v>
@@ -1638,7 +1638,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>3.779163122177124</v>
+        <v>3.774311542510986</v>
       </c>
       <c r="C11" s="1">
         <v>588</v>
@@ -1664,7 +1664,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2">
-        <v>3.624911546707153</v>
+        <v>3.620258092880249</v>
       </c>
       <c r="C12" s="1">
         <v>564</v>
@@ -1690,7 +1690,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>3.43209719657898</v>
+        <v>3.427691221237183</v>
       </c>
       <c r="C13" s="1">
         <v>534</v>
@@ -1716,7 +1716,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>3.020759582519531</v>
+        <v>3.016881704330444</v>
       </c>
       <c r="C14" s="1">
         <v>470</v>
@@ -1742,7 +1742,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>2.789382457733154</v>
+        <v>2.785801410675049</v>
       </c>
       <c r="C15" s="1">
         <v>434</v>
@@ -1768,7 +1768,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>2.750819444656372</v>
+        <v>2.74728798866272</v>
       </c>
       <c r="C16" s="1">
         <v>428</v>
@@ -1794,7 +1794,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>1.851018667221069</v>
+        <v>1.848642349243164</v>
       </c>
       <c r="C17" s="1">
         <v>288</v>
@@ -1820,7 +1820,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>1.761038661003113</v>
+        <v>1.758777856826782</v>
       </c>
       <c r="C18" s="1">
         <v>274</v>
@@ -1846,7 +1846,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>1.156886696815491</v>
+        <v>1.155401468276978</v>
       </c>
       <c r="C19" s="1">
         <v>180</v>
@@ -1872,7 +1872,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>0.9640722274780273</v>
+        <v>0.9628345966339111</v>
       </c>
       <c r="C20" s="1">
         <v>150</v>
@@ -1898,7 +1898,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>0.629860520362854</v>
+        <v>0.6290519237518311</v>
       </c>
       <c r="C21" s="1">
         <v>98</v>
@@ -1924,7 +1924,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>0.617006242275238</v>
+        <v>0.6162141561508179</v>
       </c>
       <c r="C22" s="1">
         <v>96</v>
@@ -1950,7 +1950,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>0.308503121137619</v>
+        <v>0.3081070780754089</v>
       </c>
       <c r="C23" s="1">
         <v>48</v>
@@ -1976,7 +1976,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2313773334026337</v>
+        <v>0.2310802936553955</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -2002,7 +2002,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2313773334026337</v>
+        <v>0.2310802936553955</v>
       </c>
       <c r="C25" s="1">
         <v>36</v>
@@ -2028,7 +2028,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2313773334026337</v>
+        <v>0.2310802936553955</v>
       </c>
       <c r="C26" s="1">
         <v>36</v>
@@ -2054,7 +2054,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2056687474250794</v>
+        <v>0.2054047137498856</v>
       </c>
       <c r="C27" s="1">
         <v>32</v>
@@ -2080,7 +2080,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1928144544363022</v>
+        <v>0.19256691634655</v>
       </c>
       <c r="C28" s="1">
         <v>30</v>
@@ -2106,7 +2106,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1928144544363022</v>
+        <v>0.19256691634655</v>
       </c>
       <c r="C29" s="1">
         <v>30</v>
@@ -2132,7 +2132,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1928144544363022</v>
+        <v>0.19256691634655</v>
       </c>
       <c r="C30" s="1">
         <v>30</v>
@@ -2158,7 +2158,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.07712578028440476</v>
+        <v>0.07702676951885223</v>
       </c>
       <c r="C31" s="1">
         <v>12</v>
@@ -2184,7 +2184,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.05141718685626984</v>
+        <v>0.05135117843747139</v>
       </c>
       <c r="C32" s="1">
         <v>8</v>
@@ -2210,7 +2210,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>0.05141718685626984</v>
+        <v>0.05135117843747139</v>
       </c>
       <c r="C33" s="1">
         <v>8</v>
@@ -2236,7 +2236,7 @@
         <v>10</v>
       </c>
       <c r="B34" s="2">
-        <v>0.02570859342813492</v>
+        <v>0.0256755892187357</v>
       </c>
       <c r="C34" s="1">
         <v>4</v>
@@ -2262,7 +2262,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.02570859342813492</v>
+        <v>0.0256755892187357</v>
       </c>
       <c r="C35" s="1">
         <v>4</v>
